--- a/data/trans_orig/IP26D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP26D-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>10579</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>37516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58435</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>28814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>52252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>34626</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>30098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40813</t>
+          <t>39720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59798</t>
+          <t>60250</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24351</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36379</t>
+          <t>35598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28982</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48181</t>
+          <t>48148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48948</t>
+          <t>49229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63894</t>
+          <t>64224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91582</t>
+          <t>90481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102105</t>
+          <t>101555</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130250</t>
+          <t>129859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130359</t>
+          <t>129537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162876</t>
+          <t>161134</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239585</t>
+          <t>240280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281992</t>
+          <t>283103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106161</t>
+          <t>106047</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136710</t>
+          <t>136064</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111803</t>
+          <t>112490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>143513</t>
+          <t>145173</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>228965</t>
+          <t>228198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>271780</t>
+          <t>271698</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98219</t>
+          <t>99792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128153</t>
+          <t>128604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115596</t>
+          <t>114414</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145181</t>
+          <t>145835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>221950</t>
+          <t>222755</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>264684</t>
+          <t>264228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21427</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64873</t>
+          <t>66193</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34254</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52270</t>
+          <t>51576</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>84197</t>
+          <t>84212</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>111965</t>
+          <t>111176</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>34462</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53245</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45680</t>
+          <t>45019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84753</t>
+          <t>84349</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110732</t>
+          <t>112363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>49801</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71641</t>
+          <t>71114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36654</t>
+          <t>36653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54847</t>
+          <t>56191</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93469</t>
+          <t>93500</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>120877</t>
+          <t>120618</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>25560</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>17003</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31174</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28156</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46301</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41189</t>
+          <t>40090</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>63291</t>
+          <t>61307</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44483</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67943</t>
+          <t>69227</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>91930</t>
+          <t>90635</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>122267</t>
+          <t>122053</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>175866</t>
+          <t>175294</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>212457</t>
+          <t>213604</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>191652</t>
+          <t>193449</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>231775</t>
+          <t>232564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>381196</t>
+          <t>380275</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>435792</t>
+          <t>435221</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>169030</t>
+          <t>169437</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>205531</t>
+          <t>205009</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>184586</t>
+          <t>183584</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>222348</t>
+          <t>222185</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>363457</t>
+          <t>361071</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>415477</t>
+          <t>417460</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>182096</t>
+          <t>184018</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>220564</t>
+          <t>220955</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>178045</t>
+          <t>178094</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>217032</t>
+          <t>216520</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>373185</t>
+          <t>372807</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>424815</t>
+          <t>425757</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35250</t>
+          <t>34989</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>32270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24375</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51465</t>
+          <t>52430</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27861</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>32714</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51909</t>
+          <t>52623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14301</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27204</t>
+          <t>27319</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29655</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33581</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52606</t>
+          <t>52157</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28798</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25503</t>
+          <t>24930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44777</t>
+          <t>45177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29785</t>
+          <t>29663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50769</t>
+          <t>49309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64665</t>
+          <t>64800</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93168</t>
+          <t>92290</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43408</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65310</t>
+          <t>65206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45229</t>
+          <t>45292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67374</t>
+          <t>68670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94243</t>
+          <t>93639</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125859</t>
+          <t>126216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89700</t>
+          <t>90739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119287</t>
+          <t>118994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98526</t>
+          <t>98714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126706</t>
+          <t>129167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>197852</t>
+          <t>195587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240113</t>
+          <t>238805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95637</t>
+          <t>94662</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126055</t>
+          <t>125238</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88990</t>
+          <t>89585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118262</t>
+          <t>116812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>191550</t>
+          <t>190085</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>234151</t>
+          <t>234268</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104332</t>
+          <t>104027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134277</t>
+          <t>134345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125772</t>
+          <t>125004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159252</t>
+          <t>157116</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>239506</t>
+          <t>240143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282346</t>
+          <t>282938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40934</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>30685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49554</t>
+          <t>50120</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40887</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59699</t>
+          <t>60767</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>78248</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>105992</t>
+          <t>103897</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52896</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33168</t>
+          <t>33509</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52110</t>
+          <t>52723</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71720</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>98242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41316</t>
+          <t>40500</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59477</t>
+          <t>60605</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>34517</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52491</t>
+          <t>52423</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>80043</t>
+          <t>79585</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>107009</t>
+          <t>106831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15405</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>21528</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40191</t>
+          <t>41963</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40749</t>
+          <t>39891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65686</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>43727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68088</t>
+          <t>68224</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41075</t>
+          <t>42930</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64741</t>
+          <t>66788</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>124662</t>
+          <t>124198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67963</t>
+          <t>67887</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95815</t>
+          <t>96893</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>71980</t>
+          <t>71097</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>100118</t>
+          <t>100644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>147157</t>
+          <t>147250</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>185473</t>
+          <t>187438</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>151526</t>
+          <t>153502</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>188758</t>
+          <t>190078</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161610</t>
+          <t>162687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>199641</t>
+          <t>200584</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>324328</t>
+          <t>321854</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>377083</t>
+          <t>375664</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>155981</t>
+          <t>155107</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>192915</t>
+          <t>192059</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>144650</t>
+          <t>146756</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>181855</t>
+          <t>182859</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>314227</t>
+          <t>313520</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>365649</t>
+          <t>366921</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>167965</t>
+          <t>170756</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>206420</t>
+          <t>209185</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>187069</t>
+          <t>184881</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>226098</t>
+          <t>225783</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>368284</t>
+          <t>366402</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>421950</t>
+          <t>423081</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>15548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>28156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31614</t>
+          <t>31403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>47702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>20384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32999</t>
+          <t>33389</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>24066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41716</t>
+          <t>41693</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32884</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43689</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67512</t>
+          <t>68845</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>44958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45003</t>
+          <t>45906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68382</t>
+          <t>70791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76145</t>
+          <t>75583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107819</t>
+          <t>106248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110770</t>
+          <t>111397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142456</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116688</t>
+          <t>117603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149953</t>
+          <t>147423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>237094</t>
+          <t>234818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>278900</t>
+          <t>279388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124632</t>
+          <t>125736</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157066</t>
+          <t>157484</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111229</t>
+          <t>110145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>142252</t>
+          <t>142711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>244661</t>
+          <t>244902</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>289651</t>
+          <t>291167</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108418</t>
+          <t>108169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139567</t>
+          <t>138900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118728</t>
+          <t>120255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152875</t>
+          <t>151894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,47 +8965,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>25,06%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>31,65%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>258015</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>232777</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>279034</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>27,42%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>24,74%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>258015</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>237028</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>282110</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>25,19%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>18135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31780</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50616</t>
+          <t>48702</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49274</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70169</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>86546</t>
+          <t>85640</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>112463</t>
+          <t>112838</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62345</t>
+          <t>61973</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>37120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55469</t>
+          <t>56987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83844</t>
+          <t>84781</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112290</t>
+          <t>112744</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44916</t>
+          <t>46379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>65364</t>
+          <t>66746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>44160</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63497</t>
+          <t>63167</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94428</t>
+          <t>95320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122837</t>
+          <t>122318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>31934</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>54550</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26834</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47608</t>
+          <t>47894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65343</t>
+          <t>65411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96008</t>
+          <t>95790</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42170</t>
+          <t>42608</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>66088</t>
+          <t>65427</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70797</t>
+          <t>70032</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>100775</t>
+          <t>100337</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>119753</t>
+          <t>120731</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>157436</t>
+          <t>157576</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>163540</t>
+          <t>164855</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>202199</t>
+          <t>203339</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>192181</t>
+          <t>190399</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>230999</t>
+          <t>233429</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>367694</t>
+          <t>368194</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>422457</t>
+          <t>425057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>190335</t>
+          <t>188891</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>228020</t>
+          <t>227083</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>168470</t>
+          <t>167526</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>207643</t>
+          <t>206640</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>365296</t>
+          <t>368217</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>420271</t>
+          <t>424060</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>172198</t>
+          <t>173623</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>208928</t>
+          <t>209970</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182710</t>
+          <t>180930</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>223292</t>
+          <t>221297</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>365355</t>
+          <t>364792</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>419141</t>
+          <t>418312</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -11079,12 +11079,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29333</t>
+          <t>30107</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27690</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>27781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50567</t>
+          <t>50695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22774</t>
+          <t>22925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33014</t>
+          <t>31828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>19870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>22446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36869</t>
+          <t>37538</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11776,49 +11776,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9863</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>20370</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9863</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4773</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19572</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -11831,12 +11831,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>29443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20341</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65004</t>
+          <t>66943</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>31543</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85070</t>
+          <t>84556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31660</t>
+          <t>31689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55547</t>
+          <t>55690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65642</t>
+          <t>66989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96538</t>
+          <t>96449</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171624</t>
+          <t>172730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>246799</t>
+          <t>246728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186299</t>
+          <t>186905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231058</t>
+          <t>232124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>372451</t>
+          <t>372376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>462800</t>
+          <t>455819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -12213,12 +12213,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83411</t>
+          <t>82204</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120627</t>
+          <t>120671</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94730</t>
+          <t>94366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>135039</t>
+          <t>134673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>188770</t>
+          <t>188674</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>245835</t>
+          <t>245459</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12298,12 +12298,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78125</t>
+          <t>76398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114530</t>
+          <t>114196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>87037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124880</t>
+          <t>123021</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179129</t>
+          <t>173696</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>230180</t>
+          <t>225476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -12556,12 +12556,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -12669,12 +12669,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12684,12 +12684,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32252</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>17341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24787</t>
+          <t>25163</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>37506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43353</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60771</t>
+          <t>61146</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49465</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73216</t>
+          <t>74920</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98951</t>
+          <t>97506</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128201</t>
+          <t>128422</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>30077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47679</t>
+          <t>47213</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>39116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60434</t>
+          <t>61128</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72497</t>
+          <t>72822</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100073</t>
+          <t>100631</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -13121,12 +13121,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30159</t>
+          <t>31536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>49733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47187</t>
+          <t>45224</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61551</t>
+          <t>60414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89231</t>
+          <t>89423</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27585</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20340</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41406</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13436,12 +13436,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32351</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37555</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92624</t>
+          <t>94357</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59719</t>
+          <t>58846</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115420</t>
+          <t>113200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45648</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71854</t>
+          <t>70673</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>51977</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>81285</t>
+          <t>82747</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>102731</t>
+          <t>105207</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>143943</t>
+          <t>145044</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238243</t>
+          <t>236024</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>332470</t>
+          <t>315070</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>265934</t>
+          <t>264303</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>316569</t>
+          <t>318067</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>516019</t>
+          <t>513833</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>615510</t>
+          <t>615980</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128611</t>
+          <t>133328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>174833</t>
+          <t>177192</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13818,12 +13818,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147955</t>
+          <t>145542</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>195412</t>
+          <t>195334</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>292332</t>
+          <t>292808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>359023</t>
+          <t>357470</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -13916,12 +13916,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124160</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>169937</t>
+          <t>170033</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>132651</t>
+          <t>135591</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>178012</t>
+          <t>180820</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>274693</t>
+          <t>273772</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>333245</t>
+          <t>335408</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
